--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 72,2%</t>
+        <v>7</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,24 +1048,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1192,17 +1192,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,25 +1339,25 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,25 +1489,25 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▲ 148,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,25 +1789,25 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,7%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,25 +1939,25 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 188,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1975,19 +1975,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2089,33 +2089,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 211,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2125,19 +2125,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,33 +2239,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 85,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2275,19 +2275,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2389,25 +2389,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2539,33 +2539,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 610,3%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2839,33 +2839,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2989,33 +2989,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3139,33 +3139,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 195,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3298,24 +3298,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3589,33 +3589,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 164,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3739,33 +3739,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3889,33 +3889,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4039,33 +4039,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4082,12 +4082,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4189,33 +4189,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,9%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4339,33 +4339,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4489,33 +4489,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+        <v>6</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4639,33 +4639,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 607,7%</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4789,33 +4789,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>18</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4939,33 +4939,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>25</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5089,33 +5089,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>32</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5239,33 +5239,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,1%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5392,30 +5392,30 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5539,33 +5539,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5694,20 +5694,20 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5732,12 +5732,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5839,33 +5839,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,8%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5989,33 +5989,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6139,33 +6139,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6182,82 +6182,532 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>7</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,0%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 72,2%</t>
+        <v>9</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1339,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>5</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>17</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1939,33 +1939,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2089,33 +2089,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 148,2%</t>
+          <t>R$ 188,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2239,33 +2239,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,7%</t>
+          <t>R$ 211,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>24</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2389,33 +2389,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 302,4%</t>
+          <t>R$ 85,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>19</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2425,19 +2425,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2509,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2539,33 +2539,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>22</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,14 +2659,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+        <v>12</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,14 +2809,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2839,33 +2839,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,9%</t>
+        <v>17</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,14 +2959,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2989,33 +2989,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 610,3%</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,0%</t>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3109,14 +3109,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3139,33 +3139,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3259,14 +3259,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3289,33 +3289,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3409,14 +3409,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3439,33 +3439,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 195,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,14 +3559,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3589,33 +3589,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,14 +3709,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3748,24 +3748,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3859,14 +3859,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3898,11 +3898,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,14 +4009,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4042,17 +4042,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4082,12 +4082,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4159,14 +4159,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4189,33 +4189,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4309,14 +4309,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4339,33 +4339,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4459,14 +4459,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4489,33 +4489,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,14 +4609,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4639,33 +4639,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,9%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,14 +4759,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4789,33 +4789,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4909,14 +4909,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4939,33 +4939,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,9%</t>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5059,14 +5059,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5089,33 +5089,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 607,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5209,14 +5209,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5239,33 +5239,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5359,14 +5359,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5389,33 +5389,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5509,14 +5509,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5542,22 +5542,22 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>20</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5659,14 +5659,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5689,33 +5689,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,1%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5809,14 +5809,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5839,25 +5839,25 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5959,14 +5959,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5989,33 +5989,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6109,14 +6109,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6139,33 +6139,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6259,14 +6259,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6289,33 +6289,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6332,12 +6332,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6409,14 +6409,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6439,33 +6439,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6559,14 +6559,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6589,33 +6589,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6632,82 +6632,232 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,22 +592,22 @@
           <t>R$ 47,00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>11</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>9</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,2%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1648,24 +1648,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>18</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2089,25 +2089,25 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,33 +2239,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 148,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2389,25 +2389,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2539,25 +2539,25 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 302,4%</t>
+          <t>R$ 188,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2575,19 +2575,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 211,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>24</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2725,19 +2725,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2839,33 +2839,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 85,00</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+        <v>19</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2875,19 +2875,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2989,25 +2989,25 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,9%</t>
+        <v>22</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3139,33 +3139,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 610,3%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,0%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3289,33 +3289,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3439,33 +3439,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3589,33 +3589,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>22</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3739,33 +3739,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 195,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3898,24 +3898,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4042,17 +4042,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4082,12 +4082,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4189,33 +4189,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 164,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4339,33 +4339,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4489,33 +4489,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4639,33 +4639,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4789,33 +4789,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,9%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4939,33 +4939,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5089,33 +5089,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,9%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5239,33 +5239,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 197,00</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>▲ 607,7%</t>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5389,33 +5389,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>18</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5539,33 +5539,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,8%</t>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5689,33 +5689,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,4%</t>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5839,33 +5839,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,1%</t>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5992,30 +5992,30 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6139,33 +6139,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6292,22 +6292,22 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6332,12 +6332,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6439,33 +6439,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+        <v>14</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6589,33 +6589,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,4%</t>
+        <v>12</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6739,33 +6739,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6782,82 +6782,532 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 141,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -892,22 +892,22 @@
           <t>R$ 94,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>18</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1042,22 +1042,22 @@
           <t>R$ 47,00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 72,2%</t>
+        <v>7</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,33 +1939,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2098,24 +2098,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2242,17 +2242,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>5</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2389,25 +2389,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2539,25 +2539,25 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 148,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2839,25 +2839,25 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,7%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2989,25 +2989,25 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 188,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3139,33 +3139,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 211,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3175,19 +3175,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3289,33 +3289,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 85,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3325,19 +3325,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3439,25 +3439,25 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3589,33 +3589,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 610,3%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3739,33 +3739,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3889,33 +3889,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4039,33 +4039,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4082,12 +4082,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4189,33 +4189,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 195,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4348,24 +4348,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4492,17 +4492,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4639,33 +4639,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 164,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4789,33 +4789,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4939,33 +4939,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5089,33 +5089,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5239,33 +5239,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,9%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5389,33 +5389,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5539,33 +5539,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+        <v>6</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5689,33 +5689,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 607,7%</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5839,33 +5839,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>18</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5989,33 +5989,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>25</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6139,33 +6139,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>32</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6289,33 +6289,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,1%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6332,12 +6332,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6442,30 +6442,30 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6589,33 +6589,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6744,20 +6744,20 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6782,12 +6782,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6889,33 +6889,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,8%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7039,33 +7039,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7189,33 +7189,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7232,82 +7232,532 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 141,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,2%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 141,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 157,1%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1342,22 +1342,22 @@
           <t>R$ 94,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1939,33 +1939,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2089,33 +2089,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2239,33 +2239,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 72,2%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2389,33 +2389,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2509,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2539,33 +2539,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>18</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,14 +2659,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,14 +2809,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2839,33 +2839,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>11</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,14 +2959,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2989,33 +2989,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3109,14 +3109,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3139,33 +3139,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
+          <t>R$ 188,00</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>▲ 148,2%</t>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3259,14 +3259,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3289,33 +3289,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
+          <t>R$ 211,00</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>▼ 49,7%</t>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3409,14 +3409,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3439,33 +3439,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 85,00</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3475,19 +3475,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,14 +3559,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3589,33 +3589,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,14 +3709,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3739,33 +3739,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3859,14 +3859,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3889,33 +3889,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,14 +4009,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4039,33 +4039,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 127,00</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>▲ 610,3%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4082,12 +4082,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4159,14 +4159,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4189,33 +4189,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>22</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4309,14 +4309,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4339,33 +4339,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4459,14 +4459,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4489,33 +4489,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 195,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>33</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,14 +4609,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4639,33 +4639,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,14 +4759,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4798,24 +4798,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4909,14 +4909,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4948,11 +4948,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5059,14 +5059,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5092,17 +5092,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5209,14 +5209,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5239,33 +5239,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5359,14 +5359,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5389,33 +5389,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5509,14 +5509,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5539,33 +5539,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5659,14 +5659,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5689,33 +5689,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,9%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5809,14 +5809,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5839,33 +5839,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5959,14 +5959,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5989,33 +5989,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+        <v>18</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6109,14 +6109,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6139,33 +6139,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▲ 607,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6259,14 +6259,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6289,33 +6289,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6332,12 +6332,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6409,14 +6409,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6439,33 +6439,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6559,14 +6559,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6592,22 +6592,22 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6709,14 +6709,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6739,33 +6739,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,1%</t>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6859,14 +6859,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6889,25 +6889,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7009,14 +7009,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7039,33 +7039,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7159,14 +7159,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7189,33 +7189,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7309,14 +7309,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7339,33 +7339,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7459,14 +7459,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7489,33 +7489,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7532,12 +7532,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7609,14 +7609,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7639,33 +7639,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7682,82 +7682,232 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,22 +592,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,2%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 141,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 70,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>16</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,25 +1039,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 141,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 157,1%</t>
+        <v>19</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1342,22 +1342,22 @@
           <t>R$ 94,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 72,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 47,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 47,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>9</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2092,17 +2092,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>14</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2248,16 +2248,16 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,0%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2392,17 +2392,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,2%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2539,20 +2539,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>9</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2561,11 +2561,11 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2839,33 +2839,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2989,33 +2989,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3139,33 +3139,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3289,33 +3289,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>▲ 148,2%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3409,12 +3409,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3439,33 +3439,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,7%</t>
+          <t>R$ 188,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>16</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3589,33 +3589,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 302,4%</t>
+          <t>R$ 211,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>24</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3625,19 +3625,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3739,33 +3739,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 85,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>19</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3775,19 +3775,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3889,33 +3889,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+        <v>22</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4039,33 +4039,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,9%</t>
+        <v>12</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4082,12 +4082,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4189,33 +4189,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▲ 610,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,0%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4339,33 +4339,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4489,33 +4489,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4639,33 +4639,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
+          <t>R$ 195,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4798,24 +4798,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>33</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4942,17 +4942,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5107,15 +5107,15 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5242,15 +5242,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5282,12 +5282,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5389,33 +5389,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>17</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5539,33 +5539,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5689,33 +5689,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5839,33 +5839,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,9%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5989,20 +5989,20 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6011,11 +6011,11 @@
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6139,33 +6139,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 197,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,9%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6289,33 +6289,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 607,7%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6332,12 +6332,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6439,33 +6439,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>25</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6589,33 +6589,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,8%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6632,12 +6632,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6739,33 +6739,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>▲ 49,4%</t>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>20</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6889,33 +6889,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,1%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7042,17 +7042,17 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7061,11 +7061,11 @@
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7189,33 +7189,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7339,25 +7339,25 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>14</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7492,22 +7492,22 @@
           <t>R$ 39,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+        <v>12</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -7532,12 +7532,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7639,33 +7639,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7792,22 +7792,22 @@
           <t>R$ 39,00</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7832,82 +7832,382 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,51 +670,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,25 +735,25 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -812,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -820,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -832,39 +826,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,25 +881,25 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 70,2%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,8%</t>
+        <v>10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -915,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1031,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 141,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,24 +1040,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>24</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1151,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1192,17 +1184,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,33 +1331,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 43,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
           <t>▲ 100,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 157,1%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1451,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,33 +1481,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1601,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,33 +1631,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1674,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1751,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,33 +1781,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1824,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1901,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,25 +1931,25 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▲ 122,2%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1965,7 +1957,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1974,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2051,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2089,33 +2081,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2124,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2201,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,33 +2231,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2274,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2351,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2389,33 +2381,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2424,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2501,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2539,25 +2531,25 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2565,7 +2557,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2574,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2651,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2689,33 +2681,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 72,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2724,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,12 +2801,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2839,25 +2831,25 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 141,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>19</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2865,7 +2857,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,12 +2874,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,12 +2951,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2989,33 +2981,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3032,12 +3024,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3109,12 +3101,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3139,33 +3131,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3182,12 +3174,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3259,12 +3251,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3289,33 +3281,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3332,12 +3324,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3409,12 +3401,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3439,33 +3431,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3482,12 +3474,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,12 +3551,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3589,33 +3581,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 148,2%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3632,12 +3624,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,12 +3701,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3739,33 +3731,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,7%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,6%</t>
+        <v>9</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3782,12 +3774,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3859,12 +3851,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3889,33 +3881,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3925,19 +3917,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,12 +4001,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4039,7 +4031,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4048,16 +4040,16 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4065,7 +4057,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4075,19 +4067,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4159,12 +4151,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4192,17 +4184,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+        <v>11</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4225,19 +4217,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4309,12 +4301,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4339,33 +4331,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4375,19 +4367,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4459,12 +4451,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4489,33 +4481,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>▲ 610,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4525,19 +4517,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,12 +4601,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4639,33 +4631,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4675,19 +4667,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4759,12 +4751,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4789,7 +4781,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
+          <t>R$ 156,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4798,24 +4790,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4825,19 +4817,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4909,12 +4901,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4942,17 +4934,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4975,19 +4967,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5059,12 +5051,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5089,33 +5081,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5125,19 +5117,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5209,12 +5201,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5239,33 +5231,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 188,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5275,19 +5267,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5359,12 +5351,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5389,33 +5381,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 211,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>24</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5425,19 +5417,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5509,12 +5501,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5539,33 +5531,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 85,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5575,19 +5567,19 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5659,12 +5651,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5689,25 +5681,25 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>22</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5715,7 +5707,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5732,12 +5724,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5809,12 +5801,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5839,33 +5831,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5882,12 +5874,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5959,12 +5951,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5989,33 +5981,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6032,12 +6024,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6109,12 +6101,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6139,33 +6131,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 127,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,9%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6182,12 +6174,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6259,12 +6251,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6289,33 +6281,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 28,0%</t>
+        <v>22</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6332,12 +6324,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6409,12 +6401,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6439,33 +6431,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6482,12 +6474,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6559,12 +6551,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6589,33 +6581,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 607,7%</t>
+          <t>R$ 195,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6632,12 +6624,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6709,12 +6701,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6739,33 +6731,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>30</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6782,12 +6774,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6859,12 +6851,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6889,25 +6881,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>18</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6915,7 +6907,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6932,12 +6924,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7009,12 +7001,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7039,33 +7031,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7082,12 +7074,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7159,12 +7151,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7189,33 +7181,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>17</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7232,12 +7224,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7309,12 +7301,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7339,33 +7331,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7382,12 +7374,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7459,12 +7451,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7489,33 +7481,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 158,00</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7532,12 +7524,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7609,12 +7601,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7642,7 +7634,7 @@
           <t>R$ 79,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>▲ 102,6%</t>
         </is>
@@ -7650,9 +7642,9 @@
       <c r="I96" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7682,12 +7674,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7759,12 +7751,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7792,22 +7784,22 @@
           <t>R$ 39,00</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+        <v>6</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7815,7 +7807,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7832,12 +7824,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7909,12 +7901,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7939,33 +7931,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▲ 21,4%</t>
+        <v>21</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7982,12 +7974,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8059,12 +8051,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8089,7 +8081,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8098,24 +8090,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8132,82 +8124,1882 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,9%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 607,7%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,8%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,1%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,4%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,47 +670,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -771,19 +775,19 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,8 +820,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -826,37 +832,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 120,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -917,19 +925,19 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1001,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 242,9%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1067,19 +1075,19 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1151,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1181,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 56,2%</t>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1217,19 +1225,19 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1301,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1331,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 130,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1367,19 +1375,19 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1451,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1481,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 47,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1517,19 +1525,19 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1601,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1631,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,4%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,19 +1675,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1751,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1781,25 +1789,25 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1807,7 +1815,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1817,19 +1825,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1901,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1931,25 +1939,25 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 122,2%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1957,7 +1965,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1967,19 +1975,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2051,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2081,25 +2089,25 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,1%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2107,7 +2115,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2117,19 +2125,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2201,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2231,12 +2239,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -2244,20 +2252,20 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2267,19 +2275,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2351,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2381,33 +2389,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,6%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2424,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2501,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2531,7 +2539,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2540,16 +2548,16 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>13</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 44,4%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2557,7 +2565,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2574,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2604,7 +2612,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2612,10 +2620,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2624,39 +2630,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2681,25 +2685,25 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,2%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,8%</t>
+        <v>9</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2707,7 +2711,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2724,12 +2728,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2754,7 +2758,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2762,51 +2766,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 141,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2840,24 +2840,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2912,10 +2912,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2924,39 +2922,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2984,17 +2980,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3024,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3101,12 +3097,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3131,33 +3127,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 157,1%</t>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3174,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3251,12 +3247,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3281,33 +3277,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3324,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3401,12 +3397,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3431,33 +3427,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 173,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 72,7%</t>
+        <v>16</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3474,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3551,12 +3547,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3581,33 +3577,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3624,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3654,7 +3650,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3662,10 +3658,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3674,39 +3668,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3731,33 +3723,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3774,12 +3766,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3804,7 +3796,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3812,51 +3804,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3881,33 +3869,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3924,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3954,7 +3942,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3962,10 +3950,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3974,39 +3960,37 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4031,25 +4015,25 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>10</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4057,7 +4041,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4074,12 +4058,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4151,12 +4135,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4181,33 +4165,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4224,12 +4208,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4301,12 +4285,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4331,33 +4315,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 80,0%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4374,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4451,12 +4435,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4481,33 +4465,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4524,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4601,12 +4585,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4631,25 +4615,25 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -4657,7 +4641,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4674,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4751,12 +4735,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4781,33 +4765,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,4%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4824,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4901,12 +4885,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4931,33 +4915,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>18</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4974,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5051,12 +5035,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5081,33 +5065,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▲ 122,2%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5124,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5201,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5231,33 +5215,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,1%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5274,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5351,12 +5335,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5381,33 +5365,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 148,2%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5424,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5501,12 +5485,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5531,12 +5515,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,7%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -5544,20 +5528,20 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5574,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5651,12 +5635,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5681,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 302,4%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>18</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5717,19 +5701,19 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5801,12 +5785,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5834,22 +5818,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 70,2%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 29,4%</t>
+        <v>16</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5857,7 +5841,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5867,19 +5851,19 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5951,12 +5935,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5981,33 +5965,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 141,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,8%</t>
+        <v>19</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6017,19 +6001,19 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6101,12 +6085,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6131,33 +6115,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,9%</t>
+        <v>15</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6167,19 +6151,19 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6251,12 +6235,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6281,33 +6265,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 610,3%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,0%</t>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6317,19 +6301,19 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6401,12 +6385,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6431,25 +6415,25 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>7</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6457,7 +6441,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6467,19 +6451,19 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6551,12 +6535,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6581,25 +6565,25 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6607,7 +6591,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6617,19 +6601,19 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6701,12 +6685,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6731,33 +6715,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6767,19 +6751,19 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6851,12 +6835,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6881,7 +6865,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
+          <t>R$ 47,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6890,24 +6874,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6917,19 +6901,19 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7001,12 +6985,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7034,17 +7018,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7067,19 +7051,19 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7151,12 +7135,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7181,7 +7165,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7190,24 +7174,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7217,19 +7201,19 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7301,12 +7285,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7334,17 +7318,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7367,19 +7351,19 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7451,12 +7435,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7481,33 +7465,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7517,19 +7501,19 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7601,12 +7585,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7631,33 +7615,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7667,19 +7651,19 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7751,12 +7735,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7781,33 +7765,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7817,19 +7801,19 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7901,12 +7885,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7931,33 +7915,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,9%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>17</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7967,19 +7951,19 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8051,12 +8035,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8081,33 +8065,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8117,19 +8101,19 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8201,12 +8185,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8231,33 +8215,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+        <v>13</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8267,19 +8251,19 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8351,12 +8335,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8381,20 +8365,20 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 188,00</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>▲ 607,7%</t>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8403,11 +8387,11 @@
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8417,19 +8401,19 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8501,12 +8485,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8531,33 +8515,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 211,00</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>24</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8567,19 +8551,19 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8651,12 +8635,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8681,33 +8665,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 85,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+        <v>19</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8717,19 +8701,19 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8801,12 +8785,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8831,25 +8815,25 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>22</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
@@ -8857,7 +8841,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8874,12 +8858,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8951,12 +8935,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8981,33 +8965,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,1%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9024,12 +9008,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9101,12 +9085,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9131,33 +9115,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>17</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9174,12 +9158,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9251,12 +9235,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9281,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9324,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9401,12 +9385,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9431,33 +9415,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>22</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9474,12 +9458,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9551,12 +9535,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9584,22 +9568,22 @@
           <t>R$ 39,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+        <v>25</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
@@ -9607,7 +9591,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9624,12 +9608,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9701,12 +9685,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9731,33 +9715,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+          <t>R$ 195,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21,4%</t>
+        <v>33</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9774,12 +9758,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9851,12 +9835,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9881,33 +9865,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9924,82 +9908,3232 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 164,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>23,8%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,9%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▲ 607,7%</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 4,8%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>15,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▲ 49,4%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,1%</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,5%</t>
+        <v>19</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -889,25 +889,25 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 11,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -915,7 +915,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1344,20 +1344,20 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 130,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 47,4%</t>
+          <t>▲ 130,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,8%</t>
+        <v>10</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 242,9%</t>
+          <t>▼ 20,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1939,25 +1939,25 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2089,25 +2089,25 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2242,17 +2242,17 @@
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2389,33 +2389,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,8%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2425,19 +2425,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2509,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2539,33 +2539,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 44,4%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,14 +2582,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2620,8 +2620,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2630,39 +2632,41 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2690,20 +2694,20 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▲ 44,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2728,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2769,9 +2773,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2801,14 +2805,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2840,24 +2844,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2874,14 +2878,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2913,11 +2917,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2947,14 +2951,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2986,11 +2990,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3020,14 +3024,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3050,7 +3054,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3058,10 +3062,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3070,41 +3072,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3130,17 +3130,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3247,14 +3247,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3277,33 +3277,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3397,14 +3397,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3427,33 +3427,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 173,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 173,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3586,24 +3586,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,14 +3620,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3658,8 +3658,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3668,39 +3670,41 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3726,9 +3730,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
@@ -3736,7 +3740,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3766,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3807,9 +3811,9 @@
       <c r="I45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3839,14 +3843,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3869,33 +3873,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3912,14 +3916,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3951,11 +3955,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3985,14 +3989,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4015,25 +4019,25 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -4041,7 +4045,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4058,14 +4062,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4096,10 +4100,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4108,41 +4110,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4170,20 +4170,20 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▲ 242,9%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4208,12 +4208,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4285,14 +4285,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4315,33 +4315,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▼ 56,2%</t>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4435,14 +4435,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4465,33 +4465,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4585,14 +4585,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4615,33 +4615,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 43,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
           <t>▲ 100,0%</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4735,14 +4735,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4765,33 +4765,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,4%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4885,14 +4885,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4915,25 +4915,25 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,4%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4958,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5035,14 +5035,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5074,16 +5074,16 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▲ 122,2%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,14 +5185,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5218,22 +5218,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,1%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 122,2%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,14 +5335,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5365,33 +5365,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 75,1%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5485,14 +5485,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5515,33 +5515,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,6%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,14 +5635,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5674,16 +5674,16 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>19</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
@@ -5708,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5785,14 +5785,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5818,22 +5818,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 70,2%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5858,12 +5858,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5935,14 +5935,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5965,33 +5965,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 141,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,2%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6085,14 +6085,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6115,33 +6115,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 141,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6235,14 +6235,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6265,33 +6265,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 157,1%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6308,12 +6308,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6385,14 +6385,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6415,33 +6415,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6535,14 +6535,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6565,33 +6565,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6685,14 +6685,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6718,22 +6718,22 @@
           <t>R$ 94,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
@@ -6758,12 +6758,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6835,14 +6835,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6865,33 +6865,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6985,14 +6985,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7015,33 +7015,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7135,14 +7135,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7165,33 +7165,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7285,14 +7285,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7315,33 +7315,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7435,14 +7435,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7465,33 +7465,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7585,14 +7585,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7615,33 +7615,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▼ 72,2%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7658,12 +7658,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7735,14 +7735,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7765,33 +7765,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7885,14 +7885,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7915,33 +7915,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>18</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8035,14 +8035,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8065,33 +8065,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8185,14 +8185,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8215,33 +8215,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>11</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8335,14 +8335,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8365,33 +8365,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8485,14 +8485,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8515,33 +8515,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
+          <t>R$ 188,00</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>▲ 148,2%</t>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8635,14 +8635,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8665,33 +8665,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
+          <t>R$ 211,00</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>▼ 49,7%</t>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8785,14 +8785,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8815,33 +8815,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 85,00</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8851,19 +8851,19 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,14 +8935,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8965,33 +8965,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9085,14 +9085,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9115,33 +9115,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9235,14 +9235,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9265,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9385,14 +9385,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9415,33 +9415,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 127,00</t>
         </is>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>▲ 610,3%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9535,14 +9535,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9565,33 +9565,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>22</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9685,14 +9685,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9715,33 +9715,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9835,14 +9835,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9865,33 +9865,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 195,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>33</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9985,14 +9985,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10015,33 +10015,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10058,12 +10058,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10135,14 +10135,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10174,24 +10174,24 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10285,14 +10285,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10324,11 +10324,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10435,14 +10435,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10468,17 +10468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10585,14 +10585,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10615,33 +10615,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10735,14 +10735,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10765,33 +10765,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10808,12 +10808,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10885,14 +10885,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10915,33 +10915,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11035,14 +11035,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11065,33 +11065,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,9%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11108,12 +11108,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11185,14 +11185,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11215,33 +11215,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11335,14 +11335,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11365,33 +11365,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+        <v>18</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11408,12 +11408,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11485,14 +11485,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11515,33 +11515,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>▲ 607,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11635,14 +11635,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11665,33 +11665,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11785,14 +11785,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11815,33 +11815,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11858,12 +11858,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11935,14 +11935,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11968,22 +11968,22 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12085,14 +12085,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12115,33 +12115,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,1%</t>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12235,14 +12235,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12265,25 +12265,25 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12385,14 +12385,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12415,33 +12415,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12458,12 +12458,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12535,14 +12535,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12565,33 +12565,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12685,14 +12685,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12715,33 +12715,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12758,12 +12758,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12835,14 +12835,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12865,33 +12865,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12985,14 +12985,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -13015,33 +13015,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13058,82 +13058,232 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 87,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 17,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 17,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,5%</t>
+        <v>19</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 17,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1039,25 +1039,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 11,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1339,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1494,20 +1494,20 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 130,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 47,4%</t>
+          <t>▲ 130,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,8%</t>
+        <v>10</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 47,4%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1939,33 +1939,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 242,9%</t>
+          <t>▼ 20,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2089,25 +2089,25 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2239,25 +2239,25 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2392,17 +2392,17 @@
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2509,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2539,33 +2539,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,8%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2575,19 +2575,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,14 +2659,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▲ 44,4%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,14 +2732,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2770,8 +2770,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2780,39 +2782,41 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2840,20 +2844,20 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▲ 44,4%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2878,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2919,9 +2923,9 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2951,14 +2955,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2981,7 +2985,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2990,24 +2994,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3024,14 +3028,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3063,11 +3067,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3097,14 +3101,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3136,11 +3140,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3170,14 +3174,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3200,7 +3204,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3208,10 +3212,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3220,41 +3222,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3280,17 +3280,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3397,14 +3397,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3427,33 +3427,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3577,33 +3577,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 173,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3697,14 +3697,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 173,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3736,24 +3736,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,14 +3770,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3808,8 +3808,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3818,39 +3820,41 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3876,9 +3880,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
@@ -3886,7 +3890,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3916,12 +3920,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3957,9 +3961,9 @@
       <c r="I47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3989,14 +3993,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4019,33 +4023,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4062,14 +4066,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4101,11 +4105,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4135,14 +4139,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4165,25 +4169,25 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4191,7 +4195,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4208,14 +4212,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4238,7 +4242,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4246,10 +4250,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4258,41 +4260,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4320,20 +4320,20 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 242,9%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4358,12 +4358,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4435,14 +4435,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4465,33 +4465,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 56,2%</t>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4585,14 +4585,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4615,33 +4615,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4735,14 +4735,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4765,33 +4765,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 43,00</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
           <t>▲ 100,0%</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4885,14 +4885,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4915,33 +4915,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,4%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5035,14 +5035,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5065,25 +5065,25 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▲ 2,4%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5108,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,14 +5185,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5224,16 +5224,16 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 122,2%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,14 +5335,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5368,22 +5368,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,1%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 122,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5485,14 +5485,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5515,33 +5515,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 75,1%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,14 +5635,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5665,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,6%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5785,14 +5785,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5824,16 +5824,16 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>19</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5858,12 +5858,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5935,14 +5935,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5968,22 +5968,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 70,2%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -6008,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6085,14 +6085,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6115,33 +6115,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 141,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 70,2%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6235,14 +6235,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6265,33 +6265,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 141,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6308,12 +6308,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6385,14 +6385,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6415,33 +6415,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 157,1%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6535,14 +6535,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6565,33 +6565,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6685,14 +6685,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6715,33 +6715,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6835,14 +6835,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6868,22 +6868,22 @@
           <t>R$ 94,00</t>
         </is>
       </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6908,12 +6908,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6985,14 +6985,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7015,33 +7015,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7135,14 +7135,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7165,33 +7165,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7285,14 +7285,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7315,33 +7315,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7435,14 +7435,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7465,33 +7465,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7585,14 +7585,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7615,33 +7615,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7658,12 +7658,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7735,14 +7735,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7765,33 +7765,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 72,2%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7885,14 +7885,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7915,33 +7915,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8035,14 +8035,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8065,33 +8065,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>18</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8185,14 +8185,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8215,33 +8215,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8335,14 +8335,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8365,33 +8365,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>11</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8485,14 +8485,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8515,33 +8515,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8635,14 +8635,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8665,33 +8665,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
+          <t>R$ 188,00</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>▲ 148,2%</t>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8785,14 +8785,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8815,33 +8815,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
+          <t>R$ 211,00</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,7%</t>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,14 +8935,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8965,33 +8965,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 85,00</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9001,19 +9001,19 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9085,14 +9085,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9115,33 +9115,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9235,14 +9235,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9265,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9385,14 +9385,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9415,33 +9415,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9535,14 +9535,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9565,33 +9565,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 127,00</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>▲ 610,3%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9685,14 +9685,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9715,33 +9715,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>22</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9835,14 +9835,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9865,33 +9865,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9985,14 +9985,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10015,33 +10015,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 195,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>33</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10058,12 +10058,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10135,14 +10135,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10165,33 +10165,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10285,14 +10285,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10324,24 +10324,24 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10435,14 +10435,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10474,11 +10474,11 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10585,14 +10585,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10618,17 +10618,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10735,14 +10735,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10765,33 +10765,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10808,12 +10808,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10885,14 +10885,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10915,33 +10915,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11035,14 +11035,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11065,33 +11065,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11108,12 +11108,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11185,14 +11185,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11215,33 +11215,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,9%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11335,14 +11335,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11365,33 +11365,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11408,12 +11408,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11485,14 +11485,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11515,33 +11515,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+        <v>18</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11635,14 +11635,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11665,33 +11665,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
-          <t>▲ 607,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11785,14 +11785,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11815,33 +11815,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11858,12 +11858,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11935,14 +11935,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11965,33 +11965,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12085,14 +12085,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12118,22 +12118,22 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12235,14 +12235,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12265,33 +12265,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,1%</t>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12385,14 +12385,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12415,25 +12415,25 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12458,12 +12458,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12535,14 +12535,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12565,33 +12565,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12685,14 +12685,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12715,33 +12715,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12758,12 +12758,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12835,14 +12835,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12865,33 +12865,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12985,14 +12985,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -13015,33 +13015,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13135,14 +13135,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -13165,33 +13165,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13208,82 +13208,232 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -589,25 +589,25 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 87,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 44,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,4%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 38,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -739,33 +739,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 87,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▲ 17,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 17,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,5%</t>
+        <v>19</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1189,25 +1189,25 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 11,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1339,33 +1339,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1489,33 +1489,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,7%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1644,20 +1644,20 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 130,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1789,33 +1789,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▼ 47,4%</t>
+          <t>▲ 130,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -1939,33 +1939,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,8%</t>
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,4%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2089,33 +2089,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 242,9%</t>
+          <t>▼ 20,8%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2239,25 +2239,25 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2389,25 +2389,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2509,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2542,17 +2542,17 @@
           <t>R$ 40,00</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,14 +2659,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▼ 30,8%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2725,19 +2725,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,14 +2809,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2839,33 +2839,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 44,4%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2882,14 +2882,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2920,8 +2920,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2930,39 +2932,41 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -2990,20 +2994,20 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▲ 44,4%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -3028,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3069,9 +3073,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3101,14 +3105,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3131,7 +3135,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 40,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3140,24 +3144,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3174,14 +3178,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3213,11 +3217,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3247,14 +3251,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3286,11 +3290,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3320,14 +3324,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3350,7 +3354,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3358,10 +3362,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3370,41 +3372,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3430,17 +3430,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3577,33 +3577,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3697,14 +3697,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3727,33 +3727,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 173,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3847,14 +3847,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 173,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3886,24 +3886,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>16</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,14 +3920,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3958,8 +3958,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3968,39 +3970,41 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4026,9 +4030,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
@@ -4036,7 +4040,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4066,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4107,9 +4111,9 @@
       <c r="I49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4139,14 +4143,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4169,33 +4173,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4212,14 +4216,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4251,11 +4255,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4285,14 +4289,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4315,25 +4319,25 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4341,7 +4345,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4358,14 +4362,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4388,7 +4392,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4396,10 +4400,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4408,41 +4410,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4470,20 +4470,20 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▲ 242,9%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4508,12 +4508,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4585,14 +4585,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4615,33 +4615,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 56,2%</t>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4735,14 +4735,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4765,33 +4765,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4885,14 +4885,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -4915,33 +4915,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 43,00</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
           <t>▲ 100,0%</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5035,14 +5035,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5065,33 +5065,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 2,4%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,14 +5185,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5215,25 +5215,25 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 2,4%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,14 +5335,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5374,16 +5374,16 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▲ 122,2%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5485,14 +5485,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5518,22 +5518,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,1%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 122,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,14 +5635,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5665,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 75,1%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5785,14 +5785,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5815,33 +5815,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,6%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5935,14 +5935,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -5974,16 +5974,16 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 12,5%</t>
+        <v>19</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -6008,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6085,14 +6085,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6118,22 +6118,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 70,2%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6158,12 +6158,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6235,14 +6235,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6265,33 +6265,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 141,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 70,2%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6308,12 +6308,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6385,14 +6385,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6415,33 +6415,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 141,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6535,14 +6535,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6565,33 +6565,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 157,1%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6685,14 +6685,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6715,33 +6715,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6835,14 +6835,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -6865,33 +6865,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6985,14 +6985,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7018,22 +7018,22 @@
           <t>R$ 94,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -7058,12 +7058,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7135,14 +7135,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7165,33 +7165,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▼ 35,7%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7285,14 +7285,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7315,33 +7315,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 47,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7435,14 +7435,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7465,33 +7465,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7585,14 +7585,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7615,33 +7615,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7658,12 +7658,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7735,14 +7735,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7765,33 +7765,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7885,14 +7885,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -7915,33 +7915,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>▼ 72,2%</t>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8035,14 +8035,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8065,33 +8065,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8185,14 +8185,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8215,33 +8215,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 78,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▲ 54,5%</t>
+        <v>18</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8335,14 +8335,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8365,33 +8365,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8485,14 +8485,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8515,33 +8515,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,8%</t>
+        <v>11</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8635,14 +8635,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8665,33 +8665,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,9%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8785,14 +8785,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8815,33 +8815,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
+          <t>R$ 188,00</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>▲ 148,2%</t>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,14 +8935,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -8965,33 +8965,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
+          <t>R$ 211,00</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>▼ 49,7%</t>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9085,14 +9085,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9115,33 +9115,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 85,00</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9151,19 +9151,19 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9235,14 +9235,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9265,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9385,14 +9385,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9415,33 +9415,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9535,14 +9535,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9565,33 +9565,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9685,14 +9685,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9715,33 +9715,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 127,00</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>▲ 610,3%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 12,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9835,14 +9835,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -9865,33 +9865,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 277,00</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,2%</t>
+        <v>22</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9985,14 +9985,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10015,33 +10015,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10058,12 +10058,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10135,14 +10135,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10165,33 +10165,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 195,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>33</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10285,14 +10285,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10315,33 +10315,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10435,14 +10435,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 164,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10474,24 +10474,24 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10585,14 +10585,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10624,11 +10624,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10735,14 +10735,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10768,17 +10768,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10808,12 +10808,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10885,14 +10885,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -10915,33 +10915,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▲ 26,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11035,14 +11035,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11065,33 +11065,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11108,12 +11108,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11185,14 +11185,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11215,33 +11215,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▼ 71,4%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11335,14 +11335,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11365,33 +11365,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,9%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11408,12 +11408,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11485,14 +11485,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11515,33 +11515,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11635,14 +11635,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11665,33 +11665,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+        <v>18</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11785,14 +11785,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11815,33 +11815,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>▲ 607,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11858,12 +11858,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11935,14 +11935,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -11965,33 +11965,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 276,00</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>32</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12085,14 +12085,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12115,33 +12115,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,8%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12235,14 +12235,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12268,22 +12268,22 @@
           <t>R$ 118,00</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,5%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12385,14 +12385,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12415,33 +12415,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,1%</t>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▲ 35,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12458,12 +12458,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12535,14 +12535,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12565,25 +12565,25 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12685,14 +12685,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12715,33 +12715,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,6%</t>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12758,12 +12758,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12835,14 +12835,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -12865,33 +12865,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12985,14 +12985,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -13015,33 +13015,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13135,14 +13135,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -13165,33 +13165,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
+          <t>R$ 39,00</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>▲ 202,6%</t>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13285,14 +13285,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-026</t>
@@ -13315,33 +13315,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13358,82 +13358,232 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
+++ b/saida_skus/SKU_UTD-026-PORTA-LENCO-FUME.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,25 +589,25 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 44,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,4%</t>
+          <t>▼ 1,1%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 38,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,28 +744,28 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 87,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 97,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,25 +1039,25 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 17,5%</t>
+          <t>R$ 44,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 17,4%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 44,00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 49,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,5%</t>
+        <v>25</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 38,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
+          <t>R$ 87,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1348,24 +1348,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,0%</t>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,33 +1639,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 17,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
           <t>R$ 80,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 130,0%</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,33 +1939,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 120,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 47,4%</t>
+        <v>26</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2089,33 +2089,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 160,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,8%</t>
+          <t>▼ 36,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,33 +2239,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 120,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 242,9%</t>
+          <t>▲ 8,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2392,30 +2392,30 @@
           <t>R$ 80,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 130,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2539,33 +2539,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 47,4%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2689,33 +2689,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 160,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2839,33 +2839,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 80,00</t>
+          <t>R$ 120,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>24</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2875,19 +2875,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2989,25 +2989,25 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 40,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 44,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3070,8 +3070,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3080,37 +3082,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3140,20 +3144,20 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -3161,7 +3165,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3171,19 +3175,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3208,7 +3212,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3216,47 +3220,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3281,33 +3289,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 42,9%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3317,19 +3325,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3354,7 +3362,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3362,8 +3370,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>1</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3372,37 +3382,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3427,33 +3439,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 80,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3470,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3547,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3577,33 +3589,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 44,4%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3620,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3650,7 +3662,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3658,10 +3670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3670,39 +3680,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3727,33 +3735,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,3%</t>
+          <t>R$ 40,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3770,12 +3778,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3800,7 +3808,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3808,51 +3816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3877,7 +3881,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 173,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3886,24 +3890,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 23,1%</t>
+          <t>▲ 42,9%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3920,12 +3924,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3950,7 +3954,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3958,10 +3962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3970,39 +3972,37 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4036,11 +4036,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4108,8 +4108,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4118,37 +4120,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4182,11 +4186,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4216,12 +4220,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4246,7 +4250,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4254,47 +4258,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4319,33 +4327,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 50,3%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4362,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4392,7 +4400,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4400,8 +4408,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>1</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4410,37 +4420,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4465,33 +4477,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 173,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>16</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 23,1%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4508,12 +4520,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4585,12 +4597,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4615,7 +4627,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4624,24 +4636,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 242,9%</t>
+        <v>13</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4658,12 +4670,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4688,7 +4700,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4696,10 +4708,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4708,39 +4718,37 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4774,11 +4782,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 56,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4808,12 +4816,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4838,7 +4846,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4846,51 +4854,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4924,16 +4928,16 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4958,12 +4962,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4988,7 +4992,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4996,10 +5000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5008,39 +5010,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5068,30 +5068,30 @@
           <t>R$ 86,00</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5215,25 +5215,25 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 43,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 2,4%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>24</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 242,9%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5365,33 +5365,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 56,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5485,12 +5485,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5515,25 +5515,25 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 43,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 122,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5635,12 +5635,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5665,33 +5665,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,1%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5815,33 +5815,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 43,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▲ 302,4%</t>
+          <t>▲ 2,4%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,1%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5974,16 +5974,16 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,6%</t>
+        <v>18</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -6008,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6085,12 +6085,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6124,16 +6124,16 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 12,5%</t>
+          <t>▲ 122,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6270,20 +6270,20 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▼ 70,2%</t>
+          <t>▼ 75,1%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,8%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6308,12 +6308,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6415,25 +6415,25 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 141,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6565,33 +6565,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>19</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6608,12 +6608,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -6728,20 +6728,20 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 157,1%</t>
+          <t>▲ 12,5%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6865,25 +6865,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 70,2%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,2%</t>
+          <t>▼ 15,8%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6908,12 +6908,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6985,12 +6985,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 141,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 72,7%</t>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7165,33 +7165,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>15</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7315,20 +7315,20 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 47,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 35,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 157,1%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7337,11 +7337,11 @@
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7465,33 +7465,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 47,00</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,2%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7615,33 +7615,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>19</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 72,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7658,12 +7658,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
@@ -7783,15 +7783,15 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 47,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7926,9 +7926,9 @@
       <c r="I100" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 80,0%</t>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 35,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8074,11 +8074,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 72,2%</t>
+        <v>14</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8215,33 +8215,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 78,00</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>7</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8365,33 +8365,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 156,00</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 54,5%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8515,33 +8515,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>9</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 80,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8635,12 +8635,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8665,33 +8665,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 72,2%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8815,33 +8815,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 188,00</t>
+          <t>R$ 78,00</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>18</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8965,33 +8965,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 211,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 148,2%</t>
+          <t>R$ 156,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 26,3%</t>
+          <t>▲ 54,5%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9115,33 +9115,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 85,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,6%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9265,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 302,4%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9301,19 +9301,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9415,33 +9415,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 188,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 29,4%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9451,19 +9451,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9535,12 +9535,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9565,33 +9565,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 211,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 148,2%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,8%</t>
+          <t>▲ 26,3%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9601,19 +9601,19 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9715,33 +9715,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
+          <t>R$ 85,00</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▼ 49,7%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,9%</t>
+          <t>▼ 13,6%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9751,19 +9751,19 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9865,33 +9865,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 277,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>▲ 610,3%</t>
+          <t>▲ 302,4%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 12,0%</t>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9985,12 +9985,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10015,25 +10015,25 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,2%</t>
+          <t>▼ 29,4%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
@@ -10058,12 +10058,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10135,12 +10135,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10165,33 +10165,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 195,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▲ 30,8%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10315,33 +10315,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 127,00</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,9%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10435,12 +10435,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10465,33 +10465,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 164,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 277,00</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 610,3%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10615,33 +10615,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 24,2%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10735,12 +10735,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 195,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10774,24 +10774,24 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>33</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10808,12 +10808,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10924,11 +10924,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>30</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11035,12 +11035,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11065,25 +11065,25 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 158,00</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 164,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 26,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11108,12 +11108,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11185,12 +11185,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11215,33 +11215,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 102,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11335,12 +11335,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11365,33 +11365,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 71,4%</t>
+        <v>17</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11408,12 +11408,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11485,12 +11485,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11515,33 +11515,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 197,00</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11635,12 +11635,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11665,25 +11665,25 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 158,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26,7%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11785,12 +11785,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11815,33 +11815,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,9%</t>
+        <v>15</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11858,12 +11858,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11965,33 +11965,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 276,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 607,7%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 71,4%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12115,33 +12115,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,9%</t>
+          <t>R$ 197,00</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,9%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>21</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12235,12 +12235,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12270,20 +12270,20 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,8%</t>
+          <t>▼ 28,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12308,12 +12308,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12415,33 +12415,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 49,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,5%</t>
+        <v>25</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,9%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12458,12 +12458,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12535,12 +12535,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12565,33 +12565,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,1%</t>
+          <t>R$ 276,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 607,7%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 35,7%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12608,12 +12608,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12685,12 +12685,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12715,33 +12715,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 118,00</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 202,6%</t>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12758,12 +12758,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12835,12 +12835,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12865,33 +12865,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,6%</t>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 4,8%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13015,33 +13015,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 79,00</t>
+          <t>R$ 118,00</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>▲ 102,6%</t>
+          <t>▲ 49,4%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>21</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,5%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13135,12 +13135,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13165,33 +13165,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 39,00</t>
+          <t>R$ 79,00</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,9%</t>
+          <t>▼ 33,1%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+        <v>19</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 35,7%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13285,12 +13285,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13324,24 +13324,24 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>▲ 21,4%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13358,12 +13358,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13435,12 +13435,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13468,22 +13468,22 @@
           <t>R$ 39,00</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,6%</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13508,82 +13508,682 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 79,00</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>▲ 102,6%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,9%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 118,00</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>▲ 202,6%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4502756969</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 78,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-026</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Porta Lenço Fume</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4502679247</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 46,95</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 39,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-026</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Porta Lenço Fume</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4502756969</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>R$ 78,90</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>